--- a/The Runics Alpha_Data/StreamingAssets/runics.xlsx
+++ b/The Runics Alpha_Data/StreamingAssets/runics.xlsx
@@ -1511,10 +1511,10 @@
         <v>6</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -3151,13 +3151,13 @@
         <v>5</v>
       </c>
       <c r="J109" t="s">
+        <v>24</v>
+      </c>
+      <c r="K109" t="s">
+        <v>5</v>
+      </c>
+      <c r="L109" t="s">
         <v>40</v>
-      </c>
-      <c r="K109" t="s">
-        <v>5</v>
-      </c>
-      <c r="L109" t="s">
-        <v>24</v>
       </c>
       <c r="N109" t="s">
         <v>7</v>
